--- a/BKU 2026.xlsx
+++ b/BKU 2026.xlsx
@@ -1,38 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benda\OneDrive\Desktop\FILE BENDAHARA 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\SistemLaporanBarang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129725A3-42FE-4C9F-B34E-FADDD3A34291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B591D0C-2D58-46C9-B732-F553CBF4411A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANUARI" sheetId="21" r:id="rId1"/>
     <sheet name="FEBRUARI" sheetId="5" r:id="rId2"/>
-    <sheet name="MARET" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">FEBRUARI!$A$1:$G$177</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">JANUARI!$A$1:$G$135</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">JANUARI!$6:$7</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="363">
   <si>
     <t>BUKU KAS UMUM</t>
   </si>
@@ -218,9 +223,6 @@
   </si>
   <si>
     <t xml:space="preserve">           Pengguna Anggaran,</t>
-  </si>
-  <si>
-    <t>NOV</t>
   </si>
   <si>
     <t>Potongan Lain-lain</t>
@@ -1982,60 +1984,6 @@
   </si>
   <si>
     <t>Bayar Biaya Perjalanan Dinas Luar Daerah  Dalam Rangka Mengikuti Rapat Koordinasi Diseminasi Kajian Dampak Efisiensi Anggaran terhadap Pembangunan Daerah Tertinggal di Bappelitbangda Sumba Tengah dari Sub Kegiatan Koordinasi Penyusunan Dokumen Perencanaan Pembangunan Daerah Bidang Infrastruktur (RPJPD,RPJMD dan RKPD) Tahun Anggaran 2026 kepada Charles Hermana Weru,S.Sos,dkk (GU 2)</t>
-  </si>
-  <si>
-    <t>02-03-2026</t>
-  </si>
-  <si>
-    <t>Gaji Bulan Maret  2026</t>
-  </si>
-  <si>
-    <t>Penerimaan SP2D No: 53.12/04.0/000023/LS/5.01.5.05.0.00.25.0000/M/3/2026</t>
-  </si>
-  <si>
-    <t>Penerimaan SP2D No: 53.12/04.0/000024/GU/5.01.5.05.0.00.25.0000/M/3/2026</t>
-  </si>
-  <si>
-    <t>03-03-2026</t>
-  </si>
-  <si>
-    <t>04-03-2026</t>
-  </si>
-  <si>
-    <t>05-03-2026</t>
-  </si>
-  <si>
-    <t>Penerimaan SP2D No: 53.12/04.0/000025/LS/5.01.5.05.0.00.25.0000/M/3/2026</t>
-  </si>
-  <si>
-    <t>Penerimaan SP2D No: 53.12/04.0/000026/LS/5.01.5.05.0.00.25.0000/M/3/2026</t>
-  </si>
-  <si>
-    <t>Penerimaan SP2D No: 53.12/04.0/000027/LS/5.01.5.05.0.00.25.0000/M/3/2026</t>
-  </si>
-  <si>
-    <t>Penerimaan SP2D No: 53.12/04.0/000028/LS/5.01.5.05.0.00.25.0000/M/3/2026</t>
-  </si>
-  <si>
-    <t>Bayar biaya belaja honorarium penggungjawaban pengelola keuangan bulan jan-maret 2026 kepada Arviani Asia Paulina Kore dari Sub Kegiatan Koordinasi dan Penyusunan Laporan Keuangan Bulanan/Triwulan/Semesteran SKPD Tahun Anggaran 2026.</t>
-  </si>
-  <si>
-    <t>5.01.01.2.02.5.1.1.03.07.5.1.02.02.01.0080</t>
-  </si>
-  <si>
-    <t>Bayar biaya belanja Jasa Pengelolaan BMD yang tidak Menghasilkan Pendapatan bulan jan-maret 2026 kepada Agustinus Mada Leko dari Sub Kegiatan Koordinasi dan Penyusunan Laporan Keuangan Bulanan/Triwulan/Semesteran SKPD Tahun Anggaran 2026.</t>
-  </si>
-  <si>
-    <t>5.01.01.2.02.0007.5.1.02.02.01.0001</t>
-  </si>
-  <si>
-    <t>Bayar Honorarium Penyuluh atau Pendamping Bulan Maret 2026 dari sub Kegiatan Monitoring, evaluasi dan Penyusunan Laporan Berkala Pelaksanaan Pembangunan Daerah Tahun Anggaran 2026 Kepada Elvira,dkk</t>
-  </si>
-  <si>
-    <t>Bayar biaya belanja Lembur dalam rangka verifikasi hasil usulan musrenbang kecamatan dalam aplikasi SIPD RI dari sub kegiatan Penyiapan Bahan Koordinasi Musrenbang Kecamatan Tahun Anggaran 2026 kepada Erlan Poro,dkk</t>
-  </si>
-  <si>
-    <t>5.01.02.2.01.0006.5.1.02.02.001.00071</t>
   </si>
 </sst>
 </file>
@@ -2399,7 +2347,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -2984,14 +2932,8 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3004,9 +2946,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3311,26 +3250,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="203" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="203" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="205"/>
-      <c r="C2" s="205"/>
-      <c r="D2" s="205"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
@@ -3347,7 +3286,7 @@
       </c>
       <c r="B4" s="94"/>
       <c r="C4" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D4" s="25"/>
       <c r="E4" s="25"/>
@@ -3433,10 +3372,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9" s="39"/>
       <c r="E9" s="39"/>
@@ -3449,7 +3388,7 @@
       <c r="A10" s="41"/>
       <c r="B10" s="42"/>
       <c r="C10" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" s="38"/>
       <c r="E10" s="39"/>
@@ -3838,7 +3777,7 @@
       <c r="A33" s="41"/>
       <c r="B33" s="42"/>
       <c r="C33" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
@@ -3971,7 +3910,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C41" s="37" t="s">
         <v>37</v>
@@ -3991,7 +3930,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C42" s="37" t="s">
         <v>39</v>
@@ -4011,10 +3950,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D43" s="38"/>
       <c r="E43" s="38"/>
@@ -4031,10 +3970,10 @@
         <v>5</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D44" s="39"/>
       <c r="E44" s="39">
@@ -4051,13 +3990,13 @@
         <v>6</v>
       </c>
       <c r="B45" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="85" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="66" t="s">
         <v>94</v>
-      </c>
-      <c r="C45" s="85" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="66" t="s">
-        <v>95</v>
       </c>
       <c r="E45" s="39"/>
       <c r="F45" s="38">
@@ -4073,13 +4012,13 @@
         <v>7</v>
       </c>
       <c r="B46" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C46" s="85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D46" s="66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38">
@@ -4095,13 +4034,13 @@
         <v>8</v>
       </c>
       <c r="B47" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C47" s="85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38">
@@ -4119,13 +4058,13 @@
         <v>9</v>
       </c>
       <c r="B48" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C48" s="85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38">
@@ -4141,13 +4080,13 @@
         <v>10</v>
       </c>
       <c r="B49" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C49" s="85" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D49" s="66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38">
@@ -4163,13 +4102,13 @@
         <v>11</v>
       </c>
       <c r="B50" s="70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D50" s="71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E50" s="73"/>
       <c r="F50" s="73">
@@ -4185,13 +4124,13 @@
         <v>12</v>
       </c>
       <c r="B51" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C51" s="85" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D51" s="66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38">
@@ -4207,13 +4146,13 @@
         <v>13</v>
       </c>
       <c r="B52" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C52" s="85" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38">
@@ -4229,13 +4168,13 @@
         <v>14</v>
       </c>
       <c r="B53" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C53" s="85" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D53" s="66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38">
@@ -4251,13 +4190,13 @@
         <v>15</v>
       </c>
       <c r="B54" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C54" s="85" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D54" s="66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38">
@@ -4273,13 +4212,13 @@
         <v>16</v>
       </c>
       <c r="B55" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C55" s="85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D55" s="66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38">
@@ -4295,13 +4234,13 @@
         <v>17</v>
       </c>
       <c r="B56" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C56" s="85" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D56" s="66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38">
@@ -4317,13 +4256,13 @@
         <v>18</v>
       </c>
       <c r="B57" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C57" s="63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D57" s="87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38">
@@ -4339,13 +4278,13 @@
         <v>19</v>
       </c>
       <c r="B58" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" s="85" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="68" t="s">
         <v>118</v>
-      </c>
-      <c r="D58" s="68" t="s">
-        <v>119</v>
       </c>
       <c r="E58" s="64"/>
       <c r="F58" s="38">
@@ -4361,13 +4300,13 @@
         <v>20</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" s="88" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D59" s="89" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E59" s="79"/>
       <c r="F59" s="79">
@@ -4383,13 +4322,13 @@
         <v>21</v>
       </c>
       <c r="B60" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C60" s="63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D60" s="87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38">
@@ -4405,13 +4344,13 @@
         <v>22</v>
       </c>
       <c r="B61" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C61" s="63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D61" s="87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38">
@@ -4427,13 +4366,13 @@
         <v>23</v>
       </c>
       <c r="B62" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C62" s="85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D62" s="66" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38">
@@ -4449,13 +4388,13 @@
         <v>24</v>
       </c>
       <c r="B63" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C63" s="85" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D63" s="66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38">
@@ -4471,13 +4410,13 @@
         <v>25</v>
       </c>
       <c r="B64" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" s="85" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D64" s="66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="38">
@@ -4493,13 +4432,13 @@
         <v>26</v>
       </c>
       <c r="B65" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C65" s="85" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D65" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="38">
@@ -4515,13 +4454,13 @@
         <v>27</v>
       </c>
       <c r="B66" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C66" s="85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D66" s="66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="38">
@@ -4537,13 +4476,13 @@
         <v>28</v>
       </c>
       <c r="B67" s="65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C67" s="63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D67" s="87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="38">
@@ -4559,13 +4498,13 @@
         <v>29</v>
       </c>
       <c r="B68" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C68" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="D68" s="66" t="s">
         <v>140</v>
-      </c>
-      <c r="D68" s="66" t="s">
-        <v>141</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38">
@@ -4581,13 +4520,13 @@
         <v>30</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69" s="85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D69" s="66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="38">
@@ -4603,13 +4542,13 @@
         <v>31</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C70" s="85" t="s">
+        <v>143</v>
+      </c>
+      <c r="D70" s="66" t="s">
         <v>144</v>
-      </c>
-      <c r="D70" s="66" t="s">
-        <v>145</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38">
@@ -4625,13 +4564,13 @@
         <v>32</v>
       </c>
       <c r="B71" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C71" s="85" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D71" s="66" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="38">
@@ -4647,13 +4586,13 @@
         <v>33</v>
       </c>
       <c r="B72" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C72" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="D72" s="66" t="s">
         <v>148</v>
-      </c>
-      <c r="D72" s="66" t="s">
-        <v>149</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38">
@@ -4669,13 +4608,13 @@
         <v>34</v>
       </c>
       <c r="B73" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C73" s="85" t="s">
+        <v>149</v>
+      </c>
+      <c r="D73" s="66" t="s">
         <v>150</v>
-      </c>
-      <c r="D73" s="66" t="s">
-        <v>151</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="38">
@@ -4691,13 +4630,13 @@
         <v>35</v>
       </c>
       <c r="B74" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C74" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="D74" s="66" t="s">
         <v>152</v>
-      </c>
-      <c r="D74" s="66" t="s">
-        <v>153</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="38">
@@ -4713,13 +4652,13 @@
         <v>36</v>
       </c>
       <c r="B75" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C75" s="85" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D75" s="66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="38">
@@ -4735,13 +4674,13 @@
         <v>37</v>
       </c>
       <c r="B76" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C76" s="85" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D76" s="66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="38">
@@ -4757,13 +4696,13 @@
         <v>38</v>
       </c>
       <c r="B77" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="C77" s="85" t="s">
+        <v>167</v>
+      </c>
+      <c r="D77" s="66" t="s">
         <v>99</v>
-      </c>
-      <c r="C77" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="D77" s="66" t="s">
-        <v>100</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="38">
@@ -4779,13 +4718,13 @@
         <v>39</v>
       </c>
       <c r="B78" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C78" s="85" t="s">
+        <v>119</v>
+      </c>
+      <c r="D78" s="66" t="s">
         <v>120</v>
-      </c>
-      <c r="D78" s="66" t="s">
-        <v>121</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38">
@@ -4801,13 +4740,13 @@
         <v>40</v>
       </c>
       <c r="B79" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C79" s="63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D79" s="87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E79" s="38"/>
       <c r="F79" s="38">
@@ -4823,13 +4762,13 @@
         <v>41</v>
       </c>
       <c r="B80" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C80" s="63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D80" s="87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E80" s="73"/>
       <c r="F80" s="73">
@@ -4845,13 +4784,13 @@
         <v>42</v>
       </c>
       <c r="B81" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C81" s="63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D81" s="87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E81" s="73"/>
       <c r="F81" s="73">
@@ -4867,13 +4806,13 @@
         <v>43</v>
       </c>
       <c r="B82" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C82" s="63" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D82" s="87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E82" s="38"/>
       <c r="F82" s="38">
@@ -4889,13 +4828,13 @@
         <v>44</v>
       </c>
       <c r="B83" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C83" s="63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D83" s="87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E83" s="38"/>
       <c r="F83" s="38">
@@ -4911,10 +4850,10 @@
         <v>45</v>
       </c>
       <c r="B84" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" s="90" t="s">
         <v>75</v>
-      </c>
-      <c r="C84" s="90" t="s">
-        <v>76</v>
       </c>
       <c r="D84" s="91"/>
       <c r="E84" s="39">
@@ -4931,13 +4870,13 @@
         <v>46</v>
       </c>
       <c r="B85" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C85" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="D85" s="69" t="s">
         <v>82</v>
-      </c>
-      <c r="D85" s="69" t="s">
-        <v>83</v>
       </c>
       <c r="E85" s="62"/>
       <c r="F85" s="38">
@@ -4953,10 +4892,10 @@
         <v>47</v>
       </c>
       <c r="B86" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C86" s="90" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D86" s="91"/>
       <c r="E86" s="39">
@@ -4973,13 +4912,13 @@
         <v>48</v>
       </c>
       <c r="B87" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C87" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="D87" s="91" t="s">
         <v>84</v>
-      </c>
-      <c r="D87" s="91" t="s">
-        <v>85</v>
       </c>
       <c r="E87" s="39"/>
       <c r="F87" s="38">
@@ -4995,10 +4934,10 @@
         <v>49</v>
       </c>
       <c r="B88" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C88" s="90" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D88" s="91"/>
       <c r="E88" s="39">
@@ -5015,13 +4954,13 @@
         <v>27</v>
       </c>
       <c r="B89" s="76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C89" s="92" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D89" s="77" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E89" s="78"/>
       <c r="F89" s="79">
@@ -5082,10 +5021,10 @@
         <v>51</v>
       </c>
       <c r="B95" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C95" s="90" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D95" s="91"/>
       <c r="E95" s="39">
@@ -5102,13 +5041,13 @@
         <v>52</v>
       </c>
       <c r="B96" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C96" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="D96" s="66" t="s">
         <v>88</v>
-      </c>
-      <c r="D96" s="66" t="s">
-        <v>89</v>
       </c>
       <c r="E96" s="39"/>
       <c r="F96" s="38">
@@ -5124,10 +5063,10 @@
         <v>53</v>
       </c>
       <c r="B97" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C97" s="90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D97" s="91"/>
       <c r="E97" s="39">
@@ -5144,13 +5083,13 @@
         <v>54</v>
       </c>
       <c r="B98" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C98" s="85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D98" s="66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E98" s="39"/>
       <c r="F98" s="38">
@@ -5166,10 +5105,10 @@
         <v>55</v>
       </c>
       <c r="B99" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C99" s="90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D99" s="91"/>
       <c r="E99" s="39">
@@ -5186,13 +5125,13 @@
         <v>56</v>
       </c>
       <c r="B100" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C100" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="D100" s="66" t="s">
         <v>86</v>
-      </c>
-      <c r="D100" s="66" t="s">
-        <v>87</v>
       </c>
       <c r="E100" s="38"/>
       <c r="F100" s="38">
@@ -5208,13 +5147,13 @@
         <v>57</v>
       </c>
       <c r="B101" s="70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C101" s="86" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D101" s="71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E101" s="38"/>
       <c r="F101" s="72">
@@ -5230,10 +5169,10 @@
         <v>58</v>
       </c>
       <c r="B102" s="98" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C102" s="99" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D102" s="95"/>
       <c r="E102" s="96">
@@ -5250,10 +5189,10 @@
         <v>59</v>
       </c>
       <c r="B103" s="98" t="s">
+        <v>168</v>
+      </c>
+      <c r="C103" s="100" t="s">
         <v>169</v>
-      </c>
-      <c r="C103" s="100" t="s">
-        <v>170</v>
       </c>
       <c r="D103" s="95"/>
       <c r="E103" s="97">
@@ -5270,13 +5209,13 @@
         <v>60</v>
       </c>
       <c r="B104" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C104" s="101" t="s">
+        <v>172</v>
+      </c>
+      <c r="D104" s="102" t="s">
         <v>173</v>
-      </c>
-      <c r="D104" s="102" t="s">
-        <v>174</v>
       </c>
       <c r="E104" s="97"/>
       <c r="F104" s="64">
@@ -5292,13 +5231,13 @@
         <v>61</v>
       </c>
       <c r="B105" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C105" s="101" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D105" s="102" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E105" s="97"/>
       <c r="F105" s="64">
@@ -5314,13 +5253,13 @@
         <v>62</v>
       </c>
       <c r="B106" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C106" s="101" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D106" s="102" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E106" s="97"/>
       <c r="F106" s="64">
@@ -5336,10 +5275,10 @@
         <v>63</v>
       </c>
       <c r="B107" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C107" s="100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D107" s="95"/>
       <c r="E107" s="97">
@@ -5356,13 +5295,13 @@
         <v>64</v>
       </c>
       <c r="B108" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C108" s="103" t="s">
+        <v>176</v>
+      </c>
+      <c r="D108" s="106" t="s">
         <v>177</v>
-      </c>
-      <c r="D108" s="106" t="s">
-        <v>178</v>
       </c>
       <c r="E108" s="104"/>
       <c r="F108" s="107">
@@ -5378,13 +5317,13 @@
         <v>65</v>
       </c>
       <c r="B109" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C109" s="103" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D109" s="106" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E109" s="104"/>
       <c r="F109" s="107">
@@ -5400,10 +5339,10 @@
         <v>66</v>
       </c>
       <c r="B110" s="98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C110" s="100" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D110" s="95"/>
       <c r="E110" s="97">
@@ -5420,13 +5359,13 @@
         <v>67</v>
       </c>
       <c r="B111" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C111" s="103" t="s">
+        <v>179</v>
+      </c>
+      <c r="D111" s="102" t="s">
         <v>180</v>
-      </c>
-      <c r="D111" s="102" t="s">
-        <v>181</v>
       </c>
       <c r="E111" s="97"/>
       <c r="F111" s="64">
@@ -5442,13 +5381,13 @@
         <v>68</v>
       </c>
       <c r="B112" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C112" s="103" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D112" s="102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E112" s="97"/>
       <c r="F112" s="64">
@@ -5464,13 +5403,13 @@
         <v>69</v>
       </c>
       <c r="B113" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C113" s="103" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D113" s="102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E113" s="97"/>
       <c r="F113" s="64">
@@ -5486,13 +5425,13 @@
         <v>70</v>
       </c>
       <c r="B114" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C114" s="103" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D114" s="102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E114" s="97"/>
       <c r="F114" s="64">
@@ -5508,13 +5447,13 @@
         <v>71</v>
       </c>
       <c r="B115" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C115" s="103" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D115" s="102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E115" s="97"/>
       <c r="F115" s="64">
@@ -5530,13 +5469,13 @@
         <v>72</v>
       </c>
       <c r="B116" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C116" s="103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D116" s="102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E116" s="97"/>
       <c r="F116" s="64">
@@ -5598,7 +5537,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B120" s="15"/>
       <c r="C120" s="16"/>
@@ -5613,7 +5552,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B121" s="18"/>
       <c r="C121" s="19"/>
@@ -5699,7 +5638,7 @@
       <c r="C128" s="56"/>
       <c r="D128" s="57"/>
       <c r="E128" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F128" s="57"/>
       <c r="G128" s="57"/>
@@ -5711,10 +5650,10 @@
       </c>
       <c r="C129" s="56"/>
       <c r="D129" s="57"/>
-      <c r="E129" s="206" t="s">
+      <c r="E129" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="F129" s="206"/>
+      <c r="F129" s="204"/>
       <c r="G129" s="57"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5756,12 +5695,12 @@
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="27"/>
       <c r="B134" s="59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C134" s="28"/>
       <c r="D134" s="57"/>
       <c r="E134" s="60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F134" s="60"/>
       <c r="G134" s="57"/>
@@ -5769,12 +5708,12 @@
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="26"/>
       <c r="B135" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C135" s="28"/>
       <c r="D135" s="57"/>
       <c r="E135" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F135" s="57"/>
       <c r="G135" s="57"/>
@@ -5812,26 +5751,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="206" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
+      <c r="B3" s="206"/>
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="206"/>
+      <c r="F3" s="206"/>
+      <c r="G3" s="206"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="109"/>
@@ -5848,7 +5787,7 @@
       </c>
       <c r="B5" s="113"/>
       <c r="C5" s="111" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D5" s="112"/>
       <c r="E5" s="112"/>
@@ -5931,10 +5870,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="160" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C10" s="172" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" s="161"/>
       <c r="E10" s="161"/>
@@ -5955,7 +5894,7 @@
       <c r="A11" s="162"/>
       <c r="B11" s="162"/>
       <c r="C11" s="155" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" s="163"/>
       <c r="E11" s="161"/>
@@ -6363,7 +6302,7 @@
       <c r="A34" s="154"/>
       <c r="B34" s="154"/>
       <c r="C34" s="155" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D34" s="126"/>
       <c r="E34" s="126"/>
@@ -6494,7 +6433,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="160" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C42" s="155" t="s">
         <v>37</v>
@@ -6514,7 +6453,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="160" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C43" s="155" t="s">
         <v>39</v>
@@ -6533,10 +6472,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C44" s="170" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D44" s="171"/>
       <c r="E44" s="171"/>
@@ -6553,13 +6492,13 @@
         <v>5</v>
       </c>
       <c r="B45" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C45" s="85" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E45" s="126"/>
       <c r="F45" s="126">
@@ -6575,13 +6514,13 @@
         <v>6</v>
       </c>
       <c r="B46" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C46" s="85" t="s">
+        <v>251</v>
+      </c>
+      <c r="D46" s="82" t="s">
         <v>252</v>
-      </c>
-      <c r="D46" s="82" t="s">
-        <v>253</v>
       </c>
       <c r="E46" s="125"/>
       <c r="F46" s="126">
@@ -6597,13 +6536,13 @@
         <v>7</v>
       </c>
       <c r="B47" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C47" s="85" t="s">
+        <v>251</v>
+      </c>
+      <c r="D47" s="82" t="s">
         <v>252</v>
-      </c>
-      <c r="D47" s="82" t="s">
-        <v>253</v>
       </c>
       <c r="E47" s="125"/>
       <c r="F47" s="126">
@@ -6619,13 +6558,13 @@
         <v>8</v>
       </c>
       <c r="B48" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C48" s="63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D48" s="87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E48" s="126"/>
       <c r="F48" s="126">
@@ -6641,13 +6580,13 @@
         <v>9</v>
       </c>
       <c r="B49" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C49" s="63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D49" s="87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E49" s="126"/>
       <c r="F49" s="126">
@@ -6663,13 +6602,13 @@
         <v>10</v>
       </c>
       <c r="B50" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C50" s="63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D50" s="87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E50" s="126"/>
       <c r="F50" s="126">
@@ -6685,13 +6624,13 @@
         <v>11</v>
       </c>
       <c r="B51" s="183" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C51" s="88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D51" s="89" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E51" s="184"/>
       <c r="F51" s="184">
@@ -6707,13 +6646,13 @@
         <v>12</v>
       </c>
       <c r="B52" s="186" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C52" s="187" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D52" s="188" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E52" s="189"/>
       <c r="F52" s="189">
@@ -6729,13 +6668,13 @@
         <v>13</v>
       </c>
       <c r="B53" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C53" s="63" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D53" s="87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E53" s="126"/>
       <c r="F53" s="126">
@@ -6751,13 +6690,13 @@
         <v>14</v>
       </c>
       <c r="B54" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C54" s="85" t="s">
+        <v>268</v>
+      </c>
+      <c r="D54" s="82" t="s">
         <v>269</v>
-      </c>
-      <c r="D54" s="82" t="s">
-        <v>270</v>
       </c>
       <c r="E54" s="125"/>
       <c r="F54" s="126">
@@ -6773,13 +6712,13 @@
         <v>15</v>
       </c>
       <c r="B55" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C55" s="85" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D55" s="82" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="126">
@@ -6795,13 +6734,13 @@
         <v>16</v>
       </c>
       <c r="B56" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C56" s="85" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D56" s="82" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E56" s="125"/>
       <c r="F56" s="126">
@@ -6817,13 +6756,13 @@
         <v>17</v>
       </c>
       <c r="B57" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C57" s="85" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D57" s="82" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E57" s="125"/>
       <c r="F57" s="126">
@@ -6839,13 +6778,13 @@
         <v>18</v>
       </c>
       <c r="B58" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C58" s="85" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D58" s="82" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E58" s="125"/>
       <c r="F58" s="126">
@@ -6861,13 +6800,13 @@
         <v>19</v>
       </c>
       <c r="B59" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C59" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="D59" s="82" t="s">
         <v>279</v>
-      </c>
-      <c r="D59" s="82" t="s">
-        <v>280</v>
       </c>
       <c r="E59" s="125"/>
       <c r="F59" s="126">
@@ -6883,13 +6822,13 @@
         <v>20</v>
       </c>
       <c r="B60" s="152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C60" s="85" t="s">
+        <v>280</v>
+      </c>
+      <c r="D60" s="82" t="s">
         <v>281</v>
-      </c>
-      <c r="D60" s="82" t="s">
-        <v>282</v>
       </c>
       <c r="E60" s="125"/>
       <c r="F60" s="126">
@@ -6905,13 +6844,13 @@
         <v>21</v>
       </c>
       <c r="B61" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C61" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="D61" s="82" t="s">
         <v>283</v>
-      </c>
-      <c r="D61" s="82" t="s">
-        <v>284</v>
       </c>
       <c r="E61" s="125"/>
       <c r="F61" s="126">
@@ -6927,13 +6866,13 @@
         <v>22</v>
       </c>
       <c r="B62" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C62" s="85" t="s">
+        <v>284</v>
+      </c>
+      <c r="D62" s="82" t="s">
         <v>285</v>
-      </c>
-      <c r="D62" s="82" t="s">
-        <v>286</v>
       </c>
       <c r="E62" s="125"/>
       <c r="F62" s="126">
@@ -6949,13 +6888,13 @@
         <v>23</v>
       </c>
       <c r="B63" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C63" s="85" t="s">
+        <v>286</v>
+      </c>
+      <c r="D63" s="82" t="s">
         <v>287</v>
-      </c>
-      <c r="D63" s="82" t="s">
-        <v>288</v>
       </c>
       <c r="E63" s="125"/>
       <c r="F63" s="126">
@@ -6971,13 +6910,13 @@
         <v>24</v>
       </c>
       <c r="B64" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C64" s="85" t="s">
+        <v>292</v>
+      </c>
+      <c r="D64" s="82" t="s">
         <v>293</v>
-      </c>
-      <c r="D64" s="82" t="s">
-        <v>294</v>
       </c>
       <c r="E64" s="125"/>
       <c r="F64" s="126">
@@ -6993,13 +6932,13 @@
         <v>25</v>
       </c>
       <c r="B65" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="85" t="s">
+        <v>294</v>
+      </c>
+      <c r="D65" s="82" t="s">
         <v>295</v>
-      </c>
-      <c r="D65" s="82" t="s">
-        <v>296</v>
       </c>
       <c r="E65" s="125"/>
       <c r="F65" s="126">
@@ -7015,13 +6954,13 @@
         <v>26</v>
       </c>
       <c r="B66" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C66" s="85" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D66" s="82" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E66" s="125"/>
       <c r="F66" s="126">
@@ -7037,13 +6976,13 @@
         <v>27</v>
       </c>
       <c r="B67" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C67" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="D67" s="82" t="s">
         <v>298</v>
-      </c>
-      <c r="D67" s="82" t="s">
-        <v>299</v>
       </c>
       <c r="E67" s="125"/>
       <c r="F67" s="126">
@@ -7059,13 +6998,13 @@
         <v>28</v>
       </c>
       <c r="B68" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C68" s="85" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D68" s="82" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E68" s="125"/>
       <c r="F68" s="126">
@@ -7081,13 +7020,13 @@
         <v>29</v>
       </c>
       <c r="B69" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C69" s="85" t="s">
+        <v>301</v>
+      </c>
+      <c r="D69" s="82" t="s">
         <v>302</v>
-      </c>
-      <c r="D69" s="82" t="s">
-        <v>303</v>
       </c>
       <c r="E69" s="125"/>
       <c r="F69" s="126">
@@ -7103,13 +7042,13 @@
         <v>30</v>
       </c>
       <c r="B70" s="183" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="92" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D70" s="190" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E70" s="191"/>
       <c r="F70" s="184">
@@ -7125,13 +7064,13 @@
         <v>31</v>
       </c>
       <c r="B71" s="186" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C71" s="192" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D71" s="193" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E71" s="194"/>
       <c r="F71" s="189">
@@ -7147,13 +7086,13 @@
         <v>32</v>
       </c>
       <c r="B72" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C72" s="85" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D72" s="82" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E72" s="125"/>
       <c r="F72" s="126">
@@ -7169,13 +7108,13 @@
         <v>33</v>
       </c>
       <c r="B73" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C73" s="85" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E73" s="125"/>
       <c r="F73" s="126">
@@ -7191,13 +7130,13 @@
         <v>34</v>
       </c>
       <c r="B74" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C74" s="85" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D74" s="82" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E74" s="125"/>
       <c r="F74" s="126">
@@ -7213,13 +7152,13 @@
         <v>35</v>
       </c>
       <c r="B75" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C75" s="85" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E75" s="125"/>
       <c r="F75" s="126">
@@ -7235,13 +7174,13 @@
         <v>36</v>
       </c>
       <c r="B76" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C76" s="85" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D76" s="82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E76" s="125"/>
       <c r="F76" s="126">
@@ -7257,13 +7196,13 @@
         <v>37</v>
       </c>
       <c r="B77" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C77" s="85" t="s">
+        <v>320</v>
+      </c>
+      <c r="D77" s="82" t="s">
         <v>321</v>
-      </c>
-      <c r="D77" s="82" t="s">
-        <v>322</v>
       </c>
       <c r="E77" s="125"/>
       <c r="F77" s="126">
@@ -7279,13 +7218,13 @@
         <v>38</v>
       </c>
       <c r="B78" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C78" s="85" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D78" s="82" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E78" s="125"/>
       <c r="F78" s="126">
@@ -7301,13 +7240,13 @@
         <v>39</v>
       </c>
       <c r="B79" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C79" s="85" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D79" s="82" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E79" s="125"/>
       <c r="F79" s="126">
@@ -7323,13 +7262,13 @@
         <v>40</v>
       </c>
       <c r="B80" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C80" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D80" s="82" t="s">
         <v>327</v>
-      </c>
-      <c r="D80" s="82" t="s">
-        <v>328</v>
       </c>
       <c r="E80" s="125"/>
       <c r="F80" s="126">
@@ -7345,13 +7284,13 @@
         <v>41</v>
       </c>
       <c r="B81" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C81" s="85" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D81" s="82" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E81" s="125"/>
       <c r="F81" s="126">
@@ -7367,13 +7306,13 @@
         <v>42</v>
       </c>
       <c r="B82" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C82" s="85" t="s">
+        <v>330</v>
+      </c>
+      <c r="D82" s="82" t="s">
         <v>331</v>
-      </c>
-      <c r="D82" s="82" t="s">
-        <v>332</v>
       </c>
       <c r="E82" s="125"/>
       <c r="F82" s="126">
@@ -7389,13 +7328,13 @@
         <v>43</v>
       </c>
       <c r="B83" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C83" s="85" t="s">
+        <v>332</v>
+      </c>
+      <c r="D83" s="82" t="s">
         <v>333</v>
-      </c>
-      <c r="D83" s="82" t="s">
-        <v>334</v>
       </c>
       <c r="E83" s="125"/>
       <c r="F83" s="126">
@@ -7411,13 +7350,13 @@
         <v>44</v>
       </c>
       <c r="B84" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C84" s="85" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D84" s="82" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E84" s="125"/>
       <c r="F84" s="126">
@@ -7433,13 +7372,13 @@
         <v>45</v>
       </c>
       <c r="B85" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C85" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="D85" s="82" t="s">
         <v>337</v>
-      </c>
-      <c r="D85" s="82" t="s">
-        <v>338</v>
       </c>
       <c r="E85" s="125"/>
       <c r="F85" s="126">
@@ -7455,13 +7394,13 @@
         <v>46</v>
       </c>
       <c r="B86" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C86" s="85" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D86" s="82" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E86" s="125"/>
       <c r="F86" s="126">
@@ -7477,13 +7416,13 @@
         <v>47</v>
       </c>
       <c r="B87" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C87" s="85" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D87" s="82" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E87" s="125"/>
       <c r="F87" s="126">
@@ -7499,13 +7438,13 @@
         <v>48</v>
       </c>
       <c r="B88" s="183" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C88" s="92" t="s">
+        <v>341</v>
+      </c>
+      <c r="D88" s="190" t="s">
         <v>342</v>
-      </c>
-      <c r="D88" s="190" t="s">
-        <v>343</v>
       </c>
       <c r="E88" s="191"/>
       <c r="F88" s="184">
@@ -7521,13 +7460,13 @@
         <v>49</v>
       </c>
       <c r="B89" s="186" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C89" s="192" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D89" s="193" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E89" s="194"/>
       <c r="F89" s="189">
@@ -7543,13 +7482,13 @@
         <v>50</v>
       </c>
       <c r="B90" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C90" s="85" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D90" s="82" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E90" s="125"/>
       <c r="F90" s="126">
@@ -7565,10 +7504,10 @@
         <v>51</v>
       </c>
       <c r="B91" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C91" s="173" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D91" s="176"/>
       <c r="E91" s="158">
@@ -7585,13 +7524,13 @@
         <v>52</v>
       </c>
       <c r="B92" s="152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C92" s="169" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D92" s="177" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E92" s="62"/>
       <c r="F92" s="38">
@@ -7607,13 +7546,13 @@
         <v>53</v>
       </c>
       <c r="B93" s="152" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C93" s="85" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D93" s="68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E93" s="62"/>
       <c r="F93" s="38">
@@ -7629,13 +7568,13 @@
         <v>54</v>
       </c>
       <c r="B94" s="152" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C94" s="175" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D94" s="178" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E94" s="62"/>
       <c r="F94" s="38">
@@ -7651,13 +7590,13 @@
         <v>55</v>
       </c>
       <c r="B95" s="152" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C95" s="85" t="s">
+        <v>256</v>
+      </c>
+      <c r="D95" s="68" t="s">
         <v>257</v>
-      </c>
-      <c r="D95" s="68" t="s">
-        <v>258</v>
       </c>
       <c r="E95" s="62"/>
       <c r="F95" s="38">
@@ -7691,10 +7630,10 @@
         <v>56</v>
       </c>
       <c r="B98" s="152" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C98" s="173" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D98" s="157"/>
       <c r="E98" s="158">
@@ -7711,13 +7650,13 @@
         <v>57</v>
       </c>
       <c r="B99" s="152" t="s">
+        <v>195</v>
+      </c>
+      <c r="C99" s="103" t="s">
+        <v>197</v>
+      </c>
+      <c r="D99" s="157" t="s">
         <v>196</v>
-      </c>
-      <c r="C99" s="103" t="s">
-        <v>198</v>
-      </c>
-      <c r="D99" s="157" t="s">
-        <v>197</v>
       </c>
       <c r="E99" s="125"/>
       <c r="F99" s="126">
@@ -7733,13 +7672,13 @@
         <v>58</v>
       </c>
       <c r="B100" s="152" t="s">
+        <v>195</v>
+      </c>
+      <c r="C100" s="103" t="s">
+        <v>199</v>
+      </c>
+      <c r="D100" s="157" t="s">
         <v>196</v>
-      </c>
-      <c r="C100" s="103" t="s">
-        <v>200</v>
-      </c>
-      <c r="D100" s="157" t="s">
-        <v>197</v>
       </c>
       <c r="E100" s="125"/>
       <c r="F100" s="126">
@@ -7755,13 +7694,13 @@
         <v>59</v>
       </c>
       <c r="B101" s="152" t="s">
+        <v>195</v>
+      </c>
+      <c r="C101" s="103" t="s">
+        <v>198</v>
+      </c>
+      <c r="D101" s="157" t="s">
         <v>196</v>
-      </c>
-      <c r="C101" s="103" t="s">
-        <v>199</v>
-      </c>
-      <c r="D101" s="157" t="s">
-        <v>197</v>
       </c>
       <c r="E101" s="125"/>
       <c r="F101" s="126">
@@ -7777,10 +7716,10 @@
         <v>60</v>
       </c>
       <c r="B102" s="152" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C102" s="181" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D102" s="179"/>
       <c r="E102" s="180">
@@ -7797,13 +7736,13 @@
         <v>61</v>
       </c>
       <c r="B103" s="152" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C103" s="103" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D103" s="157" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E103" s="158"/>
       <c r="F103" s="126">
@@ -7819,10 +7758,10 @@
         <v>62</v>
       </c>
       <c r="B104" s="152" t="s">
+        <v>201</v>
+      </c>
+      <c r="C104" s="181" t="s">
         <v>202</v>
-      </c>
-      <c r="C104" s="181" t="s">
-        <v>203</v>
       </c>
       <c r="D104" s="157"/>
       <c r="E104" s="158">
@@ -7839,13 +7778,13 @@
         <v>63</v>
       </c>
       <c r="B105" s="152" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C105" s="103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D105" s="157" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E105" s="158"/>
       <c r="F105" s="126">
@@ -7861,13 +7800,13 @@
         <v>64</v>
       </c>
       <c r="B106" s="152" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C106" s="103" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D106" s="154" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E106" s="153"/>
       <c r="F106" s="126">
@@ -7883,13 +7822,13 @@
         <v>65</v>
       </c>
       <c r="B107" s="183" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C107" s="195" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D107" s="182" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E107" s="196"/>
       <c r="F107" s="184">
@@ -7905,13 +7844,13 @@
         <v>66</v>
       </c>
       <c r="B108" s="186" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C108" s="197" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D108" s="185" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E108" s="198"/>
       <c r="F108" s="189">
@@ -7927,10 +7866,10 @@
         <v>67</v>
       </c>
       <c r="B109" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C109" s="181" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D109" s="154"/>
       <c r="E109" s="153">
@@ -7947,13 +7886,13 @@
         <v>68</v>
       </c>
       <c r="B110" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C110" s="103" t="s">
+        <v>213</v>
+      </c>
+      <c r="D110" s="154" t="s">
         <v>214</v>
-      </c>
-      <c r="D110" s="154" t="s">
-        <v>215</v>
       </c>
       <c r="E110" s="153"/>
       <c r="F110" s="126">
@@ -7969,13 +7908,13 @@
         <v>69</v>
       </c>
       <c r="B111" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C111" s="103" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D111" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E111" s="153"/>
       <c r="F111" s="126">
@@ -7991,13 +7930,13 @@
         <v>70</v>
       </c>
       <c r="B112" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C112" s="103" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D112" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E112" s="153"/>
       <c r="F112" s="126">
@@ -8013,13 +7952,13 @@
         <v>71</v>
       </c>
       <c r="B113" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C113" s="103" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D113" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E113" s="153"/>
       <c r="F113" s="126">
@@ -8035,13 +7974,13 @@
         <v>72</v>
       </c>
       <c r="B114" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C114" s="103" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D114" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E114" s="153"/>
       <c r="F114" s="126">
@@ -8057,13 +7996,13 @@
         <v>73</v>
       </c>
       <c r="B115" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C115" s="103" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D115" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E115" s="153"/>
       <c r="F115" s="126">
@@ -8079,10 +8018,10 @@
         <v>74</v>
       </c>
       <c r="B116" s="152" t="s">
+        <v>205</v>
+      </c>
+      <c r="C116" s="181" t="s">
         <v>206</v>
-      </c>
-      <c r="C116" s="181" t="s">
-        <v>207</v>
       </c>
       <c r="D116" s="154"/>
       <c r="E116" s="153">
@@ -8099,13 +8038,13 @@
         <v>75</v>
       </c>
       <c r="B117" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C117" s="103" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D117" s="157" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E117" s="125"/>
       <c r="F117" s="126">
@@ -8121,13 +8060,13 @@
         <v>76</v>
       </c>
       <c r="B118" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C118" s="103" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D118" s="157" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E118" s="125"/>
       <c r="F118" s="126">
@@ -8143,13 +8082,13 @@
         <v>77</v>
       </c>
       <c r="B119" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C119" s="103" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D119" s="157" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E119" s="125"/>
       <c r="F119" s="126">
@@ -8165,13 +8104,13 @@
         <v>78</v>
       </c>
       <c r="B120" s="183" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C120" s="195" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D120" s="199" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E120" s="191"/>
       <c r="F120" s="184">
@@ -8187,13 +8126,13 @@
         <v>79</v>
       </c>
       <c r="B121" s="186" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C121" s="197" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D121" s="200" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E121" s="194"/>
       <c r="F121" s="189">
@@ -8209,13 +8148,13 @@
         <v>80</v>
       </c>
       <c r="B122" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C122" s="63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D122" s="87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E122" s="126"/>
       <c r="F122" s="126">
@@ -8231,13 +8170,13 @@
         <v>81</v>
       </c>
       <c r="B123" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C123" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D123" s="87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E123" s="126"/>
       <c r="F123" s="126">
@@ -8253,13 +8192,13 @@
         <v>82</v>
       </c>
       <c r="B124" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C124" s="63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D124" s="87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E124" s="126"/>
       <c r="F124" s="126">
@@ -8275,13 +8214,13 @@
         <v>83</v>
       </c>
       <c r="B125" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C125" s="63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D125" s="87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E125" s="126"/>
       <c r="F125" s="126">
@@ -8297,13 +8236,13 @@
         <v>84</v>
       </c>
       <c r="B126" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C126" s="63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D126" s="87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E126" s="126"/>
       <c r="F126" s="126">
@@ -8319,10 +8258,10 @@
         <v>85</v>
       </c>
       <c r="B127" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C127" s="181" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D127" s="154"/>
       <c r="E127" s="153">
@@ -8339,13 +8278,13 @@
         <v>86</v>
       </c>
       <c r="B128" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C128" s="103" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D128" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E128" s="125"/>
       <c r="F128" s="126">
@@ -8361,13 +8300,13 @@
         <v>87</v>
       </c>
       <c r="B129" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C129" s="103" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D129" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E129" s="125"/>
       <c r="F129" s="126">
@@ -8383,13 +8322,13 @@
         <v>88</v>
       </c>
       <c r="B130" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C130" s="103" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D130" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E130" s="125"/>
       <c r="F130" s="126">
@@ -8405,13 +8344,13 @@
         <v>89</v>
       </c>
       <c r="B131" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C131" s="103" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D131" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E131" s="125"/>
       <c r="F131" s="126">
@@ -8427,13 +8366,13 @@
         <v>90</v>
       </c>
       <c r="B132" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C132" s="103" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D132" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E132" s="125"/>
       <c r="F132" s="126">
@@ -8449,13 +8388,13 @@
         <v>91</v>
       </c>
       <c r="B133" s="183" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C133" s="195" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D133" s="199" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E133" s="191"/>
       <c r="F133" s="201">
@@ -8471,13 +8410,13 @@
         <v>92</v>
       </c>
       <c r="B134" s="186" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C134" s="197" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D134" s="200" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E134" s="194"/>
       <c r="F134" s="189">
@@ -8493,13 +8432,13 @@
         <v>93</v>
       </c>
       <c r="B135" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C135" s="103" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D135" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E135" s="125"/>
       <c r="F135" s="126">
@@ -8515,13 +8454,13 @@
         <v>94</v>
       </c>
       <c r="B136" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C136" s="103" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D136" s="157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E136" s="125"/>
       <c r="F136" s="126">
@@ -8537,10 +8476,10 @@
         <v>95</v>
       </c>
       <c r="B137" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C137" s="181" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D137" s="154"/>
       <c r="E137" s="153">
@@ -8557,13 +8496,13 @@
         <v>96</v>
       </c>
       <c r="B138" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C138" s="103" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D138" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E138" s="126"/>
       <c r="F138" s="126">
@@ -8579,13 +8518,13 @@
         <v>97</v>
       </c>
       <c r="B139" s="152" t="s">
+        <v>225</v>
+      </c>
+      <c r="C139" s="103" t="s">
         <v>226</v>
       </c>
-      <c r="C139" s="103" t="s">
-        <v>227</v>
-      </c>
       <c r="D139" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E139" s="126"/>
       <c r="F139" s="126">
@@ -8601,13 +8540,13 @@
         <v>98</v>
       </c>
       <c r="B140" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C140" s="103" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D140" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E140" s="126"/>
       <c r="F140" s="126">
@@ -8623,13 +8562,13 @@
         <v>99</v>
       </c>
       <c r="B141" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C141" s="103" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D141" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E141" s="126"/>
       <c r="F141" s="126">
@@ -8645,13 +8584,13 @@
         <v>100</v>
       </c>
       <c r="B142" s="152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C142" s="103" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D142" s="154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E142" s="126"/>
       <c r="F142" s="126">
@@ -8667,13 +8606,13 @@
         <v>101</v>
       </c>
       <c r="B143" s="152" t="s">
+        <v>249</v>
+      </c>
+      <c r="C143" s="103" t="s">
         <v>250</v>
       </c>
-      <c r="C143" s="103" t="s">
-        <v>251</v>
-      </c>
       <c r="D143" s="154" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E143" s="126"/>
       <c r="F143" s="126">
@@ -8689,13 +8628,13 @@
         <v>102</v>
       </c>
       <c r="B144" s="152" t="s">
+        <v>288</v>
+      </c>
+      <c r="C144" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="C144" s="85" t="s">
+      <c r="D144" s="82" t="s">
         <v>290</v>
-      </c>
-      <c r="D144" s="82" t="s">
-        <v>291</v>
       </c>
       <c r="E144" s="125"/>
       <c r="F144" s="126">
@@ -8711,13 +8650,13 @@
         <v>103</v>
       </c>
       <c r="B145" s="152" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C145" s="85" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D145" s="82" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E145" s="125"/>
       <c r="F145" s="126">
@@ -8733,10 +8672,10 @@
         <v>104</v>
       </c>
       <c r="B146" s="152" t="s">
+        <v>242</v>
+      </c>
+      <c r="C146" s="181" t="s">
         <v>243</v>
-      </c>
-      <c r="C146" s="181" t="s">
-        <v>244</v>
       </c>
       <c r="D146" s="154"/>
       <c r="E146" s="153">
@@ -8753,13 +8692,13 @@
         <v>105</v>
       </c>
       <c r="B147" s="152" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C147" s="85" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D147" s="174" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E147" s="126"/>
       <c r="F147" s="126">
@@ -8775,13 +8714,13 @@
         <v>106</v>
       </c>
       <c r="B148" s="152" t="s">
+        <v>266</v>
+      </c>
+      <c r="C148" s="63" t="s">
         <v>267</v>
       </c>
-      <c r="C148" s="63" t="s">
-        <v>268</v>
-      </c>
       <c r="D148" s="87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E148" s="126"/>
       <c r="F148" s="126">
@@ -8797,13 +8736,13 @@
         <v>107</v>
       </c>
       <c r="B149" s="152" t="s">
-        <v>267</v>
-      </c>
-      <c r="C149" s="209" t="s">
-        <v>363</v>
+        <v>266</v>
+      </c>
+      <c r="C149" s="202" t="s">
+        <v>362</v>
       </c>
       <c r="D149" s="66" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E149" s="126"/>
       <c r="F149" s="126">
@@ -8819,13 +8758,13 @@
         <v>108</v>
       </c>
       <c r="B150" s="152" t="s">
+        <v>347</v>
+      </c>
+      <c r="C150" s="85" t="s">
+        <v>350</v>
+      </c>
+      <c r="D150" s="82" t="s">
         <v>348</v>
-      </c>
-      <c r="C150" s="85" t="s">
-        <v>351</v>
-      </c>
-      <c r="D150" s="82" t="s">
-        <v>349</v>
       </c>
       <c r="E150" s="125"/>
       <c r="F150" s="126">
@@ -8841,13 +8780,13 @@
         <v>109</v>
       </c>
       <c r="B151" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C151" s="85" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D151" s="82" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E151" s="125"/>
       <c r="F151" s="126">
@@ -8863,13 +8802,13 @@
         <v>110</v>
       </c>
       <c r="B152" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C152" s="85" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D152" s="82" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E152" s="125"/>
       <c r="F152" s="126">
@@ -8885,13 +8824,13 @@
         <v>111</v>
       </c>
       <c r="B153" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C153" s="85" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D153" s="82" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E153" s="125"/>
       <c r="F153" s="126">
@@ -8907,13 +8846,13 @@
         <v>112</v>
       </c>
       <c r="B154" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C154" s="85" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D154" s="82" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E154" s="125"/>
       <c r="F154" s="126">
@@ -8929,13 +8868,13 @@
         <v>113</v>
       </c>
       <c r="B155" s="152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C155" s="85" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D155" s="82" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E155" s="125"/>
       <c r="F155" s="125">
@@ -8998,7 +8937,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="138" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B159" s="139"/>
       <c r="C159" s="140"/>
@@ -9009,7 +8948,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="138" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B160" s="143"/>
       <c r="C160" s="144"/>
@@ -9102,7 +9041,7 @@
       <c r="C167" s="147"/>
       <c r="D167" s="148"/>
       <c r="E167" s="148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F167" s="148"/>
       <c r="G167" s="148"/>
@@ -9115,10 +9054,10 @@
       </c>
       <c r="C168" s="147"/>
       <c r="D168" s="148"/>
-      <c r="E168" s="207" t="s">
+      <c r="E168" s="205" t="s">
         <v>47</v>
       </c>
-      <c r="F168" s="207"/>
+      <c r="F168" s="205"/>
       <c r="G168" s="148"/>
       <c r="K168" s="2"/>
     </row>
@@ -9162,12 +9101,12 @@
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="82"/>
       <c r="B173" s="150" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C173" s="114"/>
       <c r="D173" s="148"/>
       <c r="E173" s="151" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F173" s="151"/>
       <c r="G173" s="148"/>
@@ -9175,12 +9114,12 @@
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="80"/>
       <c r="B174" s="82" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C174" s="114"/>
       <c r="D174" s="148"/>
       <c r="E174" s="148" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F174" s="148"/>
       <c r="G174" s="148"/>
@@ -9194,2602 +9133,4 @@
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="61" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:K177"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="65" customWidth="1"/>
-    <col min="4" max="4" width="32.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="208" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="208" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="109"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="113" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="D5" s="112"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="112"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="116" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="117" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="118" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="119" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="119" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="119" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="119" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="120">
-        <v>1</v>
-      </c>
-      <c r="B8" s="121">
-        <v>2</v>
-      </c>
-      <c r="C8" s="121">
-        <v>3</v>
-      </c>
-      <c r="D8" s="121">
-        <v>4</v>
-      </c>
-      <c r="E8" s="121">
-        <v>5</v>
-      </c>
-      <c r="F8" s="121">
-        <v>6</v>
-      </c>
-      <c r="G8" s="121">
-        <v>7</v>
-      </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="122"/>
-      <c r="B9" s="123"/>
-      <c r="C9" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="91"/>
-      <c r="E9" s="124">
-        <v>24406000</v>
-      </c>
-      <c r="F9" s="124"/>
-      <c r="G9" s="166">
-        <f>E9</f>
-        <v>24406000</v>
-      </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="159">
-        <v>1</v>
-      </c>
-      <c r="B10" s="160" t="s">
-        <v>364</v>
-      </c>
-      <c r="C10" s="172" t="s">
-        <v>366</v>
-      </c>
-      <c r="D10" s="161"/>
-      <c r="E10" s="161"/>
-      <c r="F10" s="161"/>
-      <c r="G10" s="167"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="162"/>
-      <c r="B11" s="162"/>
-      <c r="C11" s="155" t="s">
-        <v>365</v>
-      </c>
-      <c r="D11" s="163"/>
-      <c r="E11" s="161"/>
-      <c r="F11" s="163"/>
-      <c r="G11" s="168"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="162"/>
-      <c r="B12" s="162"/>
-      <c r="C12" s="155" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="163" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="163">
-        <v>88521800</v>
-      </c>
-      <c r="F12" s="163"/>
-      <c r="G12" s="163">
-        <f>G9+E12</f>
-        <v>112927800</v>
-      </c>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="162"/>
-      <c r="B13" s="162"/>
-      <c r="C13" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="163" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="163">
-        <v>4479448</v>
-      </c>
-      <c r="F13" s="163"/>
-      <c r="G13" s="163">
-        <f t="shared" ref="G13:G26" si="0">G12+E13</f>
-        <v>117407248</v>
-      </c>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
-      <c r="B14" s="162"/>
-      <c r="C14" s="155" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="163"/>
-      <c r="E14" s="163">
-        <v>0</v>
-      </c>
-      <c r="F14" s="163"/>
-      <c r="G14" s="163">
-        <f t="shared" si="0"/>
-        <v>117407248</v>
-      </c>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="162"/>
-      <c r="B15" s="162"/>
-      <c r="C15" s="155" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="163" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="163">
-        <v>8725000</v>
-      </c>
-      <c r="F15" s="163"/>
-      <c r="G15" s="163">
-        <f t="shared" si="0"/>
-        <v>126132248</v>
-      </c>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="155" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="126" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="126">
-        <v>3240000</v>
-      </c>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126">
-        <f t="shared" si="0"/>
-        <v>129372248</v>
-      </c>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="155" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="126" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="126">
-        <v>1465000</v>
-      </c>
-      <c r="F17" s="126"/>
-      <c r="G17" s="126">
-        <f t="shared" si="0"/>
-        <v>130837248</v>
-      </c>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="154"/>
-      <c r="B18" s="154"/>
-      <c r="C18" s="155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="126" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="126">
-        <v>4257250</v>
-      </c>
-      <c r="F18" s="126"/>
-      <c r="G18" s="126">
-        <f t="shared" si="0"/>
-        <v>135094498</v>
-      </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="154"/>
-      <c r="B19" s="154"/>
-      <c r="C19" s="155" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="126" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="126">
-        <v>3331320</v>
-      </c>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126">
-        <f t="shared" si="0"/>
-        <v>138425818</v>
-      </c>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="154"/>
-      <c r="B20" s="154"/>
-      <c r="C20" s="155" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126">
-        <f t="shared" si="0"/>
-        <v>138425818</v>
-      </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="154"/>
-      <c r="B21" s="154"/>
-      <c r="C21" s="155" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126">
-        <f t="shared" si="0"/>
-        <v>138425818</v>
-      </c>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="154"/>
-      <c r="B22" s="154"/>
-      <c r="C22" s="155" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="126" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="126">
-        <v>196625</v>
-      </c>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126">
-        <f t="shared" si="0"/>
-        <v>138622443</v>
-      </c>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="154"/>
-      <c r="B23" s="154"/>
-      <c r="C23" s="155" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126">
-        <f t="shared" si="0"/>
-        <v>138622443</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="154"/>
-      <c r="B24" s="154"/>
-      <c r="C24" s="155" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="126" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="126">
-        <v>212450</v>
-      </c>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126">
-        <f t="shared" si="0"/>
-        <v>138834893</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="154"/>
-      <c r="B25" s="154"/>
-      <c r="C25" s="155" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="126" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="126">
-        <v>637356</v>
-      </c>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126">
-        <f t="shared" si="0"/>
-        <v>139472249</v>
-      </c>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="154"/>
-      <c r="B26" s="154"/>
-      <c r="C26" s="155" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="126" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" s="126">
-        <v>1244</v>
-      </c>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126">
-        <f t="shared" si="0"/>
-        <v>139473493</v>
-      </c>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="154"/>
-      <c r="B27" s="154"/>
-      <c r="C27" s="155" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="154"/>
-      <c r="B28" s="154"/>
-      <c r="C28" s="155" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126">
-        <v>7440100</v>
-      </c>
-      <c r="G28" s="126">
-        <f>G26-F28</f>
-        <v>132033393</v>
-      </c>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="154"/>
-      <c r="B29" s="154"/>
-      <c r="C29" s="155" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="126"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="126">
-        <f>E22</f>
-        <v>196625</v>
-      </c>
-      <c r="G29" s="126">
-        <f t="shared" ref="G29:G42" si="1">G28-F29</f>
-        <v>131836768</v>
-      </c>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="154"/>
-      <c r="B30" s="154"/>
-      <c r="C30" s="155" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="126"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="126">
-        <v>0</v>
-      </c>
-      <c r="G30" s="126">
-        <f t="shared" si="1"/>
-        <v>131836768</v>
-      </c>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="154"/>
-      <c r="B31" s="154"/>
-      <c r="C31" s="155" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="126"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="126">
-        <v>0</v>
-      </c>
-      <c r="G31" s="126">
-        <f t="shared" si="1"/>
-        <v>131836768</v>
-      </c>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="154"/>
-      <c r="B32" s="154"/>
-      <c r="C32" s="155" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="126"/>
-      <c r="E32" s="126"/>
-      <c r="F32" s="126">
-        <v>0</v>
-      </c>
-      <c r="G32" s="126">
-        <f t="shared" si="1"/>
-        <v>131836768</v>
-      </c>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="154"/>
-      <c r="B33" s="154"/>
-      <c r="C33" s="155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="126"/>
-      <c r="E33" s="126"/>
-      <c r="F33" s="126">
-        <f>E18</f>
-        <v>4257250</v>
-      </c>
-      <c r="G33" s="126">
-        <f t="shared" si="1"/>
-        <v>127579518</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="154"/>
-      <c r="B34" s="154"/>
-      <c r="C34" s="155" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126">
-        <v>0</v>
-      </c>
-      <c r="G34" s="126">
-        <f t="shared" si="1"/>
-        <v>127579518</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="154"/>
-      <c r="B35" s="154"/>
-      <c r="C35" s="155" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126">
-        <v>0</v>
-      </c>
-      <c r="G35" s="126">
-        <f t="shared" si="1"/>
-        <v>127579518</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="154"/>
-      <c r="B36" s="154"/>
-      <c r="C36" s="155" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126">
-        <f>E24</f>
-        <v>212450</v>
-      </c>
-      <c r="G36" s="126">
-        <f t="shared" si="1"/>
-        <v>127367068</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="154"/>
-      <c r="B37" s="154"/>
-      <c r="C37" s="155" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126">
-        <f>E25</f>
-        <v>637356</v>
-      </c>
-      <c r="G37" s="126">
-        <f t="shared" si="1"/>
-        <v>126729712</v>
-      </c>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="154"/>
-      <c r="B38" s="154"/>
-      <c r="C38" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="126">
-        <v>1064312</v>
-      </c>
-      <c r="G38" s="126">
-        <f t="shared" si="1"/>
-        <v>125665400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="154"/>
-      <c r="B39" s="154"/>
-      <c r="C39" s="155" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
-      <c r="F39" s="126">
-        <v>0</v>
-      </c>
-      <c r="G39" s="126">
-        <f t="shared" si="1"/>
-        <v>125665400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="154"/>
-      <c r="B40" s="154"/>
-      <c r="C40" s="155" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="126">
-        <v>0</v>
-      </c>
-      <c r="G40" s="126">
-        <f t="shared" si="1"/>
-        <v>125665400</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="154"/>
-      <c r="B41" s="154"/>
-      <c r="C41" s="155" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="126"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="126">
-        <v>0</v>
-      </c>
-      <c r="G41" s="126">
-        <f t="shared" si="1"/>
-        <v>125665400</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="154">
-        <v>2</v>
-      </c>
-      <c r="B42" s="160" t="s">
-        <v>364</v>
-      </c>
-      <c r="C42" s="155" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="126"/>
-      <c r="E42" s="126"/>
-      <c r="F42" s="126">
-        <v>0</v>
-      </c>
-      <c r="G42" s="126">
-        <f t="shared" si="1"/>
-        <v>125665400</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="154">
-        <v>3</v>
-      </c>
-      <c r="B43" s="160" t="s">
-        <v>364</v>
-      </c>
-      <c r="C43" s="155" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="126"/>
-      <c r="E43" s="126" t="s">
-        <v>38</v>
-      </c>
-      <c r="F43" s="126" t="s">
-        <v>38</v>
-      </c>
-      <c r="G43" s="126"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="154">
-        <v>4</v>
-      </c>
-      <c r="B44" s="160" t="s">
-        <v>364</v>
-      </c>
-      <c r="C44" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" s="171"/>
-      <c r="E44" s="171"/>
-      <c r="F44" s="153">
-        <v>101259400</v>
-      </c>
-      <c r="G44" s="153">
-        <f>G42-F44</f>
-        <v>24406000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="154">
-        <v>5</v>
-      </c>
-      <c r="B45" s="160" t="s">
-        <v>368</v>
-      </c>
-      <c r="C45" s="172" t="s">
-        <v>367</v>
-      </c>
-      <c r="D45" s="66"/>
-      <c r="E45" s="153">
-        <v>59016200</v>
-      </c>
-      <c r="F45" s="126"/>
-      <c r="G45" s="126">
-        <f>G44+E45</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="154">
-        <v>6</v>
-      </c>
-      <c r="B46" s="152"/>
-      <c r="C46" s="85"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="125"/>
-      <c r="F46" s="126"/>
-      <c r="G46" s="126">
-        <f t="shared" ref="G46:G84" si="2">G45-F46</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="154">
-        <v>7</v>
-      </c>
-      <c r="B47" s="152"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="82"/>
-      <c r="E47" s="125"/>
-      <c r="F47" s="126"/>
-      <c r="G47" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="154">
-        <v>8</v>
-      </c>
-      <c r="B48" s="152"/>
-      <c r="C48" s="63"/>
-      <c r="D48" s="87"/>
-      <c r="E48" s="126"/>
-      <c r="F48" s="126"/>
-      <c r="G48" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="154">
-        <v>9</v>
-      </c>
-      <c r="B49" s="160" t="s">
-        <v>369</v>
-      </c>
-      <c r="C49" s="172" t="s">
-        <v>371</v>
-      </c>
-      <c r="D49" s="87"/>
-      <c r="E49" s="153">
-        <v>2310000</v>
-      </c>
-      <c r="F49" s="126"/>
-      <c r="G49" s="126">
-        <f>G48+E49</f>
-        <v>85732200</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="51" x14ac:dyDescent="0.25">
-      <c r="A50" s="154">
-        <v>10</v>
-      </c>
-      <c r="B50" s="160" t="s">
-        <v>369</v>
-      </c>
-      <c r="C50" s="63" t="s">
-        <v>375</v>
-      </c>
-      <c r="D50" s="87" t="s">
-        <v>376</v>
-      </c>
-      <c r="E50" s="153"/>
-      <c r="F50" s="126">
-        <v>2310000</v>
-      </c>
-      <c r="G50" s="126">
-        <f>G49-F50</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="154">
-        <v>13</v>
-      </c>
-      <c r="B51" s="160" t="s">
-        <v>369</v>
-      </c>
-      <c r="C51" s="172" t="s">
-        <v>372</v>
-      </c>
-      <c r="D51" s="87"/>
-      <c r="E51" s="153">
-        <v>1200000</v>
-      </c>
-      <c r="F51" s="126"/>
-      <c r="G51" s="126">
-        <f>G50+E51</f>
-        <v>84622200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="51" x14ac:dyDescent="0.25">
-      <c r="A52" s="154">
-        <v>14</v>
-      </c>
-      <c r="B52" s="160" t="s">
-        <v>369</v>
-      </c>
-      <c r="C52" s="63" t="s">
-        <v>377</v>
-      </c>
-      <c r="D52" s="82" t="s">
-        <v>378</v>
-      </c>
-      <c r="E52" s="158"/>
-      <c r="F52" s="126">
-        <v>1200000</v>
-      </c>
-      <c r="G52" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="154">
-        <v>17</v>
-      </c>
-      <c r="B53" s="160" t="s">
-        <v>370</v>
-      </c>
-      <c r="C53" s="172" t="s">
-        <v>373</v>
-      </c>
-      <c r="D53" s="82"/>
-      <c r="E53" s="158">
-        <v>5000000</v>
-      </c>
-      <c r="F53" s="126"/>
-      <c r="G53" s="126">
-        <f>G52+E53</f>
-        <v>88422200</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="154">
-        <v>18</v>
-      </c>
-      <c r="B54" s="160" t="s">
-        <v>370</v>
-      </c>
-      <c r="C54" s="169" t="s">
-        <v>379</v>
-      </c>
-      <c r="D54" s="177" t="s">
-        <v>85</v>
-      </c>
-      <c r="E54" s="158"/>
-      <c r="F54" s="126">
-        <v>5000000</v>
-      </c>
-      <c r="G54" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="154">
-        <v>20</v>
-      </c>
-      <c r="B55" s="160" t="s">
-        <v>370</v>
-      </c>
-      <c r="C55" s="172" t="s">
-        <v>374</v>
-      </c>
-      <c r="D55" s="82"/>
-      <c r="E55" s="158">
-        <v>12258000</v>
-      </c>
-      <c r="F55" s="126"/>
-      <c r="G55" s="126">
-        <f>G54+E55</f>
-        <v>95680200</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="154">
-        <v>21</v>
-      </c>
-      <c r="B56" s="160" t="s">
-        <v>370</v>
-      </c>
-      <c r="C56" s="85" t="s">
-        <v>380</v>
-      </c>
-      <c r="D56" s="82" t="s">
-        <v>381</v>
-      </c>
-      <c r="E56" s="158"/>
-      <c r="F56" s="126">
-        <v>12258000</v>
-      </c>
-      <c r="G56" s="126">
-        <f>G55-F56</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="154">
-        <v>22</v>
-      </c>
-      <c r="B57" s="152"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="82"/>
-      <c r="E57" s="158"/>
-      <c r="F57" s="126"/>
-      <c r="G57" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="154">
-        <v>23</v>
-      </c>
-      <c r="B58" s="152"/>
-      <c r="C58" s="85"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="158"/>
-      <c r="F58" s="126"/>
-      <c r="G58" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="154">
-        <v>24</v>
-      </c>
-      <c r="B59" s="152"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="126"/>
-      <c r="G59" s="126">
-        <f>G58-F59</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="154">
-        <v>25</v>
-      </c>
-      <c r="B60" s="152"/>
-      <c r="C60" s="85"/>
-      <c r="D60" s="82"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="126"/>
-      <c r="G60" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="154">
-        <v>26</v>
-      </c>
-      <c r="B61" s="152"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="82"/>
-      <c r="E61" s="158"/>
-      <c r="F61" s="126"/>
-      <c r="G61" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="154">
-        <v>27</v>
-      </c>
-      <c r="B62" s="152"/>
-      <c r="C62" s="85"/>
-      <c r="D62" s="82"/>
-      <c r="E62" s="125"/>
-      <c r="F62" s="126"/>
-      <c r="G62" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="154">
-        <v>28</v>
-      </c>
-      <c r="B63" s="152"/>
-      <c r="C63" s="85"/>
-      <c r="D63" s="82"/>
-      <c r="E63" s="125"/>
-      <c r="F63" s="126"/>
-      <c r="G63" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="154">
-        <v>29</v>
-      </c>
-      <c r="B64" s="152"/>
-      <c r="C64" s="85"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="125"/>
-      <c r="F64" s="126"/>
-      <c r="G64" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="154">
-        <v>30</v>
-      </c>
-      <c r="B65" s="152"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="82"/>
-      <c r="E65" s="125"/>
-      <c r="F65" s="126"/>
-      <c r="G65" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="154">
-        <v>31</v>
-      </c>
-      <c r="B66" s="152"/>
-      <c r="C66" s="85"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="125"/>
-      <c r="F66" s="126"/>
-      <c r="G66" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="154">
-        <v>32</v>
-      </c>
-      <c r="B67" s="152"/>
-      <c r="C67" s="85"/>
-      <c r="D67" s="82"/>
-      <c r="E67" s="125"/>
-      <c r="F67" s="126"/>
-      <c r="G67" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="154">
-        <v>33</v>
-      </c>
-      <c r="B68" s="152"/>
-      <c r="C68" s="85"/>
-      <c r="D68" s="82"/>
-      <c r="E68" s="125"/>
-      <c r="F68" s="126"/>
-      <c r="G68" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="154">
-        <v>34</v>
-      </c>
-      <c r="B69" s="152"/>
-      <c r="C69" s="85"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="125"/>
-      <c r="F69" s="126"/>
-      <c r="G69" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="154">
-        <v>35</v>
-      </c>
-      <c r="B70" s="152"/>
-      <c r="C70" s="85"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="125"/>
-      <c r="F70" s="126"/>
-      <c r="G70" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="154">
-        <v>36</v>
-      </c>
-      <c r="B71" s="152"/>
-      <c r="C71" s="85"/>
-      <c r="D71" s="82"/>
-      <c r="E71" s="125"/>
-      <c r="F71" s="126"/>
-      <c r="G71" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="154">
-        <v>37</v>
-      </c>
-      <c r="B72" s="152"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="82"/>
-      <c r="E72" s="125"/>
-      <c r="F72" s="126"/>
-      <c r="G72" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="154">
-        <v>38</v>
-      </c>
-      <c r="B73" s="152"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="125"/>
-      <c r="F73" s="126"/>
-      <c r="G73" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="154">
-        <v>39</v>
-      </c>
-      <c r="B74" s="152"/>
-      <c r="C74" s="85"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="125"/>
-      <c r="F74" s="126"/>
-      <c r="G74" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="154">
-        <v>40</v>
-      </c>
-      <c r="B75" s="152"/>
-      <c r="C75" s="85"/>
-      <c r="D75" s="82"/>
-      <c r="E75" s="125"/>
-      <c r="F75" s="126"/>
-      <c r="G75" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="154">
-        <v>41</v>
-      </c>
-      <c r="B76" s="152"/>
-      <c r="C76" s="85"/>
-      <c r="D76" s="82"/>
-      <c r="E76" s="125"/>
-      <c r="F76" s="126"/>
-      <c r="G76" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="154">
-        <v>42</v>
-      </c>
-      <c r="B77" s="152"/>
-      <c r="C77" s="85"/>
-      <c r="D77" s="82"/>
-      <c r="E77" s="125"/>
-      <c r="F77" s="126"/>
-      <c r="G77" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="154">
-        <v>43</v>
-      </c>
-      <c r="B78" s="152"/>
-      <c r="C78" s="85"/>
-      <c r="D78" s="82"/>
-      <c r="E78" s="125"/>
-      <c r="F78" s="126"/>
-      <c r="G78" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="154">
-        <v>44</v>
-      </c>
-      <c r="B79" s="152"/>
-      <c r="C79" s="85"/>
-      <c r="D79" s="82"/>
-      <c r="E79" s="125"/>
-      <c r="F79" s="126"/>
-      <c r="G79" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="154">
-        <v>45</v>
-      </c>
-      <c r="B80" s="152"/>
-      <c r="C80" s="85"/>
-      <c r="D80" s="82"/>
-      <c r="E80" s="125"/>
-      <c r="F80" s="126"/>
-      <c r="G80" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="154">
-        <v>46</v>
-      </c>
-      <c r="B81" s="152"/>
-      <c r="C81" s="85"/>
-      <c r="D81" s="82"/>
-      <c r="E81" s="125"/>
-      <c r="F81" s="126"/>
-      <c r="G81" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="154">
-        <v>47</v>
-      </c>
-      <c r="B82" s="152"/>
-      <c r="C82" s="85"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="125"/>
-      <c r="F82" s="126"/>
-      <c r="G82" s="126">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="182">
-        <v>48</v>
-      </c>
-      <c r="B83" s="183"/>
-      <c r="C83" s="92"/>
-      <c r="D83" s="190"/>
-      <c r="E83" s="191"/>
-      <c r="F83" s="184"/>
-      <c r="G83" s="184">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="185">
-        <v>49</v>
-      </c>
-      <c r="B84" s="186"/>
-      <c r="C84" s="192"/>
-      <c r="D84" s="193"/>
-      <c r="E84" s="194"/>
-      <c r="F84" s="189"/>
-      <c r="G84" s="189">
-        <f t="shared" si="2"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="154">
-        <v>50</v>
-      </c>
-      <c r="B85" s="152"/>
-      <c r="C85" s="85"/>
-      <c r="D85" s="82"/>
-      <c r="E85" s="125"/>
-      <c r="F85" s="126"/>
-      <c r="G85" s="126">
-        <f>G84-F85</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="154">
-        <v>51</v>
-      </c>
-      <c r="B86" s="152"/>
-      <c r="C86" s="173"/>
-      <c r="D86" s="176"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="153"/>
-      <c r="G86" s="126">
-        <f>G85+E86</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="154">
-        <v>52</v>
-      </c>
-      <c r="B87" s="152"/>
-      <c r="C87" s="169"/>
-      <c r="D87" s="177"/>
-      <c r="E87" s="202"/>
-      <c r="F87" s="91"/>
-      <c r="G87" s="126">
-        <f>G86-F87</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="154">
-        <v>53</v>
-      </c>
-      <c r="B88" s="152"/>
-      <c r="C88" s="85"/>
-      <c r="D88" s="68"/>
-      <c r="E88" s="202"/>
-      <c r="F88" s="91"/>
-      <c r="G88" s="126">
-        <f>G87-F88</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="154">
-        <v>54</v>
-      </c>
-      <c r="B89" s="152"/>
-      <c r="C89" s="63"/>
-      <c r="D89" s="203"/>
-      <c r="E89" s="202"/>
-      <c r="F89" s="91"/>
-      <c r="G89" s="126">
-        <f>G88-F89</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="154">
-        <v>55</v>
-      </c>
-      <c r="B90" s="152"/>
-      <c r="C90" s="85"/>
-      <c r="D90" s="68"/>
-      <c r="E90" s="202"/>
-      <c r="F90" s="91"/>
-      <c r="G90" s="126">
-        <f>G89-F90</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="154"/>
-      <c r="B91" s="152"/>
-      <c r="C91" s="85"/>
-      <c r="D91" s="68"/>
-      <c r="E91" s="202"/>
-      <c r="F91" s="91"/>
-      <c r="G91" s="126"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="154"/>
-      <c r="B92" s="152"/>
-      <c r="C92" s="85"/>
-      <c r="D92" s="68"/>
-      <c r="E92" s="202"/>
-      <c r="F92" s="91"/>
-      <c r="G92" s="126"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="154">
-        <v>56</v>
-      </c>
-      <c r="B93" s="152"/>
-      <c r="C93" s="173"/>
-      <c r="D93" s="157"/>
-      <c r="E93" s="158"/>
-      <c r="F93" s="126"/>
-      <c r="G93" s="126">
-        <f>G90+E93</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="154">
-        <v>57</v>
-      </c>
-      <c r="B94" s="152"/>
-      <c r="C94" s="103"/>
-      <c r="D94" s="157"/>
-      <c r="E94" s="125"/>
-      <c r="F94" s="126"/>
-      <c r="G94" s="126">
-        <f>G93-F94</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="154">
-        <v>58</v>
-      </c>
-      <c r="B95" s="152"/>
-      <c r="C95" s="103"/>
-      <c r="D95" s="157"/>
-      <c r="E95" s="125"/>
-      <c r="F95" s="126"/>
-      <c r="G95" s="126">
-        <f>G94-F95</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="154">
-        <v>59</v>
-      </c>
-      <c r="B96" s="152"/>
-      <c r="C96" s="103"/>
-      <c r="D96" s="157"/>
-      <c r="E96" s="125"/>
-      <c r="F96" s="126"/>
-      <c r="G96" s="126">
-        <f>G95-F96</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="154">
-        <v>60</v>
-      </c>
-      <c r="B97" s="152"/>
-      <c r="C97" s="181"/>
-      <c r="D97" s="179"/>
-      <c r="E97" s="180"/>
-      <c r="F97" s="156"/>
-      <c r="G97" s="126">
-        <f>G96+E97</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="154">
-        <v>61</v>
-      </c>
-      <c r="B98" s="152"/>
-      <c r="C98" s="103"/>
-      <c r="D98" s="157"/>
-      <c r="E98" s="158"/>
-      <c r="F98" s="126"/>
-      <c r="G98" s="126">
-        <f>G97-F98</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="154">
-        <v>62</v>
-      </c>
-      <c r="B99" s="152"/>
-      <c r="C99" s="181"/>
-      <c r="D99" s="157"/>
-      <c r="E99" s="158"/>
-      <c r="F99" s="126"/>
-      <c r="G99" s="126">
-        <f>G98+E99</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="154">
-        <v>63</v>
-      </c>
-      <c r="B100" s="152"/>
-      <c r="C100" s="103"/>
-      <c r="D100" s="157"/>
-      <c r="E100" s="158"/>
-      <c r="F100" s="126"/>
-      <c r="G100" s="126">
-        <f>G99-F100</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="154">
-        <v>64</v>
-      </c>
-      <c r="B101" s="152"/>
-      <c r="C101" s="103"/>
-      <c r="D101" s="154"/>
-      <c r="E101" s="153"/>
-      <c r="F101" s="126"/>
-      <c r="G101" s="126">
-        <f>G100-F101</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="182">
-        <v>65</v>
-      </c>
-      <c r="B102" s="183"/>
-      <c r="C102" s="195"/>
-      <c r="D102" s="182"/>
-      <c r="E102" s="196"/>
-      <c r="F102" s="184"/>
-      <c r="G102" s="184">
-        <f>G101-F102</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="185">
-        <v>66</v>
-      </c>
-      <c r="B103" s="186"/>
-      <c r="C103" s="197"/>
-      <c r="D103" s="185"/>
-      <c r="E103" s="198"/>
-      <c r="F103" s="189"/>
-      <c r="G103" s="189">
-        <f>G102-F103</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="154">
-        <v>67</v>
-      </c>
-      <c r="B104" s="152"/>
-      <c r="C104" s="181"/>
-      <c r="D104" s="154"/>
-      <c r="E104" s="153"/>
-      <c r="F104" s="126"/>
-      <c r="G104" s="126">
-        <f>G103+E104</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="154">
-        <v>68</v>
-      </c>
-      <c r="B105" s="152"/>
-      <c r="C105" s="103"/>
-      <c r="D105" s="154"/>
-      <c r="E105" s="153"/>
-      <c r="F105" s="126"/>
-      <c r="G105" s="126">
-        <f>G104-F105</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="154">
-        <v>69</v>
-      </c>
-      <c r="B106" s="152"/>
-      <c r="C106" s="103"/>
-      <c r="D106" s="154"/>
-      <c r="E106" s="153"/>
-      <c r="F106" s="126"/>
-      <c r="G106" s="126">
-        <f>G105-F106</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="154">
-        <v>70</v>
-      </c>
-      <c r="B107" s="152"/>
-      <c r="C107" s="103"/>
-      <c r="D107" s="154"/>
-      <c r="E107" s="153"/>
-      <c r="F107" s="126"/>
-      <c r="G107" s="126">
-        <f t="shared" ref="G107" si="3">G106-F107</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="154">
-        <v>71</v>
-      </c>
-      <c r="B108" s="152"/>
-      <c r="C108" s="103"/>
-      <c r="D108" s="154"/>
-      <c r="E108" s="153"/>
-      <c r="F108" s="126"/>
-      <c r="G108" s="126">
-        <f>G107-F108</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="154">
-        <v>72</v>
-      </c>
-      <c r="B109" s="152"/>
-      <c r="C109" s="103"/>
-      <c r="D109" s="154"/>
-      <c r="E109" s="153"/>
-      <c r="F109" s="126"/>
-      <c r="G109" s="126">
-        <f>G108-F109</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="154">
-        <v>73</v>
-      </c>
-      <c r="B110" s="152"/>
-      <c r="C110" s="103"/>
-      <c r="D110" s="154"/>
-      <c r="E110" s="153"/>
-      <c r="F110" s="126"/>
-      <c r="G110" s="126">
-        <f>G109-F110</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="154">
-        <v>74</v>
-      </c>
-      <c r="B111" s="152"/>
-      <c r="C111" s="181"/>
-      <c r="D111" s="154"/>
-      <c r="E111" s="153"/>
-      <c r="F111" s="126"/>
-      <c r="G111" s="126">
-        <f>G110+E111</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="154">
-        <v>75</v>
-      </c>
-      <c r="B112" s="152"/>
-      <c r="C112" s="103"/>
-      <c r="D112" s="157"/>
-      <c r="E112" s="125"/>
-      <c r="F112" s="126"/>
-      <c r="G112" s="126">
-        <f>G111-F112</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="154">
-        <v>76</v>
-      </c>
-      <c r="B113" s="152"/>
-      <c r="C113" s="103"/>
-      <c r="D113" s="157"/>
-      <c r="E113" s="125"/>
-      <c r="F113" s="126"/>
-      <c r="G113" s="126">
-        <f>G112-F113</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="154">
-        <v>77</v>
-      </c>
-      <c r="B114" s="152"/>
-      <c r="C114" s="103"/>
-      <c r="D114" s="157"/>
-      <c r="E114" s="125"/>
-      <c r="F114" s="126"/>
-      <c r="G114" s="126">
-        <f>G113-F114</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="182">
-        <v>78</v>
-      </c>
-      <c r="B115" s="183"/>
-      <c r="C115" s="195"/>
-      <c r="D115" s="199"/>
-      <c r="E115" s="191"/>
-      <c r="F115" s="184"/>
-      <c r="G115" s="184">
-        <f t="shared" ref="G115" si="4">G114-F115</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="185">
-        <v>79</v>
-      </c>
-      <c r="B116" s="186"/>
-      <c r="C116" s="197"/>
-      <c r="D116" s="200"/>
-      <c r="E116" s="194"/>
-      <c r="F116" s="189"/>
-      <c r="G116" s="189">
-        <f>G115-F116</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="154">
-        <v>80</v>
-      </c>
-      <c r="B117" s="152"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="87"/>
-      <c r="E117" s="126"/>
-      <c r="F117" s="126"/>
-      <c r="G117" s="126">
-        <f t="shared" ref="G117:G129" si="5">G116-F117</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="154">
-        <v>81</v>
-      </c>
-      <c r="B118" s="152"/>
-      <c r="C118" s="63"/>
-      <c r="D118" s="87"/>
-      <c r="E118" s="126"/>
-      <c r="F118" s="126"/>
-      <c r="G118" s="126">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="154">
-        <v>82</v>
-      </c>
-      <c r="B119" s="152"/>
-      <c r="C119" s="63"/>
-      <c r="D119" s="87"/>
-      <c r="E119" s="126"/>
-      <c r="F119" s="126"/>
-      <c r="G119" s="126">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="154">
-        <v>83</v>
-      </c>
-      <c r="B120" s="152"/>
-      <c r="C120" s="63"/>
-      <c r="D120" s="87"/>
-      <c r="E120" s="126"/>
-      <c r="F120" s="126"/>
-      <c r="G120" s="126">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="154">
-        <v>84</v>
-      </c>
-      <c r="B121" s="152"/>
-      <c r="C121" s="63"/>
-      <c r="D121" s="87"/>
-      <c r="E121" s="126"/>
-      <c r="F121" s="126"/>
-      <c r="G121" s="126">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="154">
-        <v>85</v>
-      </c>
-      <c r="B122" s="152"/>
-      <c r="C122" s="181"/>
-      <c r="D122" s="154"/>
-      <c r="E122" s="153"/>
-      <c r="F122" s="126"/>
-      <c r="G122" s="126">
-        <f>G121+E122</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="154">
-        <v>86</v>
-      </c>
-      <c r="B123" s="152"/>
-      <c r="C123" s="103"/>
-      <c r="D123" s="157"/>
-      <c r="E123" s="125"/>
-      <c r="F123" s="126"/>
-      <c r="G123" s="126">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="154">
-        <v>87</v>
-      </c>
-      <c r="B124" s="152"/>
-      <c r="C124" s="103"/>
-      <c r="D124" s="157"/>
-      <c r="E124" s="125"/>
-      <c r="F124" s="126"/>
-      <c r="G124" s="126">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="154">
-        <v>88</v>
-      </c>
-      <c r="B125" s="152"/>
-      <c r="C125" s="103"/>
-      <c r="D125" s="157"/>
-      <c r="E125" s="125"/>
-      <c r="F125" s="126"/>
-      <c r="G125" s="126">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="154">
-        <v>89</v>
-      </c>
-      <c r="B126" s="152"/>
-      <c r="C126" s="103"/>
-      <c r="D126" s="157"/>
-      <c r="E126" s="125"/>
-      <c r="F126" s="126"/>
-      <c r="G126" s="126">
-        <f>G125-F126</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="154">
-        <v>90</v>
-      </c>
-      <c r="B127" s="152"/>
-      <c r="C127" s="103"/>
-      <c r="D127" s="157"/>
-      <c r="E127" s="125"/>
-      <c r="F127" s="126"/>
-      <c r="G127" s="126">
-        <f>G126-F127</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="182">
-        <v>91</v>
-      </c>
-      <c r="B128" s="183"/>
-      <c r="C128" s="195"/>
-      <c r="D128" s="199"/>
-      <c r="E128" s="191"/>
-      <c r="F128" s="201"/>
-      <c r="G128" s="191">
-        <f>G127-F128</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="185">
-        <v>92</v>
-      </c>
-      <c r="B129" s="186"/>
-      <c r="C129" s="197"/>
-      <c r="D129" s="200"/>
-      <c r="E129" s="194"/>
-      <c r="F129" s="189"/>
-      <c r="G129" s="189">
-        <f t="shared" si="5"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="154">
-        <v>93</v>
-      </c>
-      <c r="B130" s="152"/>
-      <c r="C130" s="103"/>
-      <c r="D130" s="157"/>
-      <c r="E130" s="125"/>
-      <c r="F130" s="126"/>
-      <c r="G130" s="126">
-        <f>G129-F130</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="154">
-        <v>94</v>
-      </c>
-      <c r="B131" s="152"/>
-      <c r="C131" s="103"/>
-      <c r="D131" s="157"/>
-      <c r="E131" s="125"/>
-      <c r="F131" s="126"/>
-      <c r="G131" s="126">
-        <f>G130-F131</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="154">
-        <v>95</v>
-      </c>
-      <c r="B132" s="152"/>
-      <c r="C132" s="181"/>
-      <c r="D132" s="154"/>
-      <c r="E132" s="153"/>
-      <c r="F132" s="126"/>
-      <c r="G132" s="126">
-        <f>G131+E132</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="154">
-        <v>96</v>
-      </c>
-      <c r="B133" s="152"/>
-      <c r="C133" s="103"/>
-      <c r="D133" s="154"/>
-      <c r="E133" s="126"/>
-      <c r="F133" s="126"/>
-      <c r="G133" s="126">
-        <f>G132-F133</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="154">
-        <v>97</v>
-      </c>
-      <c r="B134" s="152"/>
-      <c r="C134" s="103"/>
-      <c r="D134" s="154"/>
-      <c r="E134" s="126"/>
-      <c r="F134" s="126"/>
-      <c r="G134" s="126">
-        <f t="shared" ref="G134:G137" si="6">G133-F134</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="154">
-        <v>98</v>
-      </c>
-      <c r="B135" s="152"/>
-      <c r="C135" s="103"/>
-      <c r="D135" s="154"/>
-      <c r="E135" s="126"/>
-      <c r="F135" s="126"/>
-      <c r="G135" s="126">
-        <f t="shared" si="6"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="154">
-        <v>99</v>
-      </c>
-      <c r="B136" s="152"/>
-      <c r="C136" s="103"/>
-      <c r="D136" s="154"/>
-      <c r="E136" s="126"/>
-      <c r="F136" s="126"/>
-      <c r="G136" s="126">
-        <f t="shared" si="6"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="154">
-        <v>100</v>
-      </c>
-      <c r="B137" s="152"/>
-      <c r="C137" s="103"/>
-      <c r="D137" s="154"/>
-      <c r="E137" s="126"/>
-      <c r="F137" s="126"/>
-      <c r="G137" s="126">
-        <f t="shared" si="6"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="154">
-        <v>101</v>
-      </c>
-      <c r="B138" s="152"/>
-      <c r="C138" s="103"/>
-      <c r="D138" s="154"/>
-      <c r="E138" s="126"/>
-      <c r="F138" s="126"/>
-      <c r="G138" s="126">
-        <f>G137-F138</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="154">
-        <v>102</v>
-      </c>
-      <c r="B139" s="152"/>
-      <c r="C139" s="85"/>
-      <c r="D139" s="82"/>
-      <c r="E139" s="125"/>
-      <c r="F139" s="126"/>
-      <c r="G139" s="126">
-        <f t="shared" ref="G139" si="7">G138-F139</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="154">
-        <v>103</v>
-      </c>
-      <c r="B140" s="152"/>
-      <c r="C140" s="85"/>
-      <c r="D140" s="82"/>
-      <c r="E140" s="125"/>
-      <c r="F140" s="126"/>
-      <c r="G140" s="126">
-        <f>G139-F140</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="154">
-        <v>104</v>
-      </c>
-      <c r="B141" s="152"/>
-      <c r="C141" s="181"/>
-      <c r="D141" s="154"/>
-      <c r="E141" s="153"/>
-      <c r="F141" s="126"/>
-      <c r="G141" s="126">
-        <f>G140+E141</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="154">
-        <v>105</v>
-      </c>
-      <c r="B142" s="152"/>
-      <c r="C142" s="85"/>
-      <c r="D142" s="174"/>
-      <c r="E142" s="126"/>
-      <c r="F142" s="126"/>
-      <c r="G142" s="126">
-        <f t="shared" ref="G142:G150" si="8">G141-F142</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="182">
-        <v>106</v>
-      </c>
-      <c r="B143" s="183"/>
-      <c r="C143" s="88"/>
-      <c r="D143" s="89"/>
-      <c r="E143" s="184"/>
-      <c r="F143" s="184"/>
-      <c r="G143" s="184">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="185">
-        <v>107</v>
-      </c>
-      <c r="B144" s="186"/>
-      <c r="C144" s="197"/>
-      <c r="D144" s="123"/>
-      <c r="E144" s="189"/>
-      <c r="F144" s="189"/>
-      <c r="G144" s="189">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="154">
-        <v>108</v>
-      </c>
-      <c r="B145" s="152"/>
-      <c r="C145" s="85"/>
-      <c r="D145" s="82"/>
-      <c r="E145" s="125"/>
-      <c r="F145" s="126"/>
-      <c r="G145" s="126">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="154">
-        <v>109</v>
-      </c>
-      <c r="B146" s="152"/>
-      <c r="C146" s="85"/>
-      <c r="D146" s="82"/>
-      <c r="E146" s="125"/>
-      <c r="F146" s="126"/>
-      <c r="G146" s="126">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="154">
-        <v>110</v>
-      </c>
-      <c r="B147" s="152"/>
-      <c r="C147" s="85"/>
-      <c r="D147" s="82"/>
-      <c r="E147" s="125"/>
-      <c r="F147" s="126"/>
-      <c r="G147" s="126">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="154">
-        <v>111</v>
-      </c>
-      <c r="B148" s="152"/>
-      <c r="C148" s="85"/>
-      <c r="D148" s="82"/>
-      <c r="E148" s="125"/>
-      <c r="F148" s="126"/>
-      <c r="G148" s="126">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="154">
-        <v>112</v>
-      </c>
-      <c r="B149" s="152"/>
-      <c r="C149" s="85"/>
-      <c r="D149" s="82"/>
-      <c r="E149" s="125"/>
-      <c r="F149" s="126"/>
-      <c r="G149" s="126">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="154">
-        <v>113</v>
-      </c>
-      <c r="B150" s="152"/>
-      <c r="C150" s="85"/>
-      <c r="D150" s="82"/>
-      <c r="E150" s="125"/>
-      <c r="F150" s="125"/>
-      <c r="G150" s="126">
-        <f t="shared" si="8"/>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="154"/>
-      <c r="B151" s="70"/>
-      <c r="C151" s="127"/>
-      <c r="D151" s="128"/>
-      <c r="E151" s="129"/>
-      <c r="F151" s="130"/>
-      <c r="G151" s="124"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="131"/>
-      <c r="B152" s="132"/>
-      <c r="C152" s="133" t="s">
-        <v>40</v>
-      </c>
-      <c r="D152" s="128"/>
-      <c r="E152" s="128">
-        <f>SUM(E9:E151)</f>
-        <v>219257693</v>
-      </c>
-      <c r="F152" s="128">
-        <f>SUM(F9:F151)</f>
-        <v>135835493</v>
-      </c>
-      <c r="G152" s="134">
-        <f>E152-F152</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="131"/>
-      <c r="B153" s="132"/>
-      <c r="C153" s="135" t="s">
-        <v>41</v>
-      </c>
-      <c r="D153" s="136"/>
-      <c r="E153" s="134">
-        <f>E152</f>
-        <v>219257693</v>
-      </c>
-      <c r="F153" s="137">
-        <f>F152+F151</f>
-        <v>135835493</v>
-      </c>
-      <c r="G153" s="134">
-        <f>E153-F153</f>
-        <v>83422200</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="138" t="s">
-        <v>192</v>
-      </c>
-      <c r="B154" s="139"/>
-      <c r="C154" s="140"/>
-      <c r="D154" s="141"/>
-      <c r="E154" s="142"/>
-      <c r="F154" s="142"/>
-      <c r="G154" s="142"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="138" t="s">
-        <v>361</v>
-      </c>
-      <c r="B155" s="143"/>
-      <c r="C155" s="144"/>
-      <c r="D155" s="145"/>
-      <c r="E155" s="145"/>
-      <c r="F155" s="145"/>
-      <c r="G155" s="145"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="82"/>
-      <c r="B156" s="143"/>
-      <c r="C156" s="144"/>
-      <c r="D156" s="145"/>
-      <c r="E156" s="145"/>
-      <c r="F156" s="145"/>
-      <c r="G156" s="145"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="82"/>
-      <c r="B157" s="81"/>
-      <c r="C157" s="114"/>
-      <c r="D157" s="146"/>
-      <c r="E157" s="146"/>
-      <c r="F157" s="146"/>
-      <c r="G157" s="146"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="82"/>
-      <c r="B158" s="82"/>
-      <c r="C158" s="147" t="s">
-        <v>42</v>
-      </c>
-      <c r="D158" s="148" t="s">
-        <v>43</v>
-      </c>
-      <c r="E158" s="148">
-        <v>4334300</v>
-      </c>
-      <c r="F158" s="148"/>
-      <c r="G158" s="148"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="82"/>
-      <c r="B159" s="82"/>
-      <c r="C159" s="147" t="s">
-        <v>44</v>
-      </c>
-      <c r="D159" s="148" t="s">
-        <v>45</v>
-      </c>
-      <c r="E159" s="148">
-        <v>20071700</v>
-      </c>
-      <c r="F159" s="148"/>
-      <c r="G159" s="148"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="82"/>
-      <c r="B160" s="82"/>
-      <c r="C160" s="147"/>
-      <c r="D160" s="149" t="s">
-        <v>46</v>
-      </c>
-      <c r="E160" s="149">
-        <f>E159+E158</f>
-        <v>24406000</v>
-      </c>
-      <c r="F160" s="148"/>
-      <c r="G160" s="148"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="82"/>
-      <c r="B161" s="82"/>
-      <c r="C161" s="114"/>
-      <c r="D161" s="148"/>
-      <c r="E161" s="148"/>
-      <c r="F161" s="148"/>
-      <c r="G161" s="148"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="82"/>
-      <c r="B162" s="82"/>
-      <c r="C162" s="147"/>
-      <c r="D162" s="148"/>
-      <c r="E162" s="148" t="s">
-        <v>191</v>
-      </c>
-      <c r="F162" s="148"/>
-      <c r="G162" s="148"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="82"/>
-      <c r="B163" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="C163" s="147"/>
-      <c r="D163" s="148"/>
-      <c r="E163" s="207" t="s">
-        <v>47</v>
-      </c>
-      <c r="F163" s="207"/>
-      <c r="G163" s="148"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="82"/>
-      <c r="B164" s="82"/>
-      <c r="C164" s="147"/>
-      <c r="D164" s="148"/>
-      <c r="E164" s="148"/>
-      <c r="F164" s="148"/>
-      <c r="G164" s="148"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="82"/>
-      <c r="B165" s="82"/>
-      <c r="C165" s="147"/>
-      <c r="D165" s="148"/>
-      <c r="E165" s="148"/>
-      <c r="F165" s="148"/>
-      <c r="G165" s="148"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="82"/>
-      <c r="B166" s="82"/>
-      <c r="C166" s="147"/>
-      <c r="D166" s="148"/>
-      <c r="E166" s="148"/>
-      <c r="F166" s="148"/>
-      <c r="G166" s="148"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="82"/>
-      <c r="B167" s="82"/>
-      <c r="C167" s="114"/>
-      <c r="D167" s="148"/>
-      <c r="E167" s="148"/>
-      <c r="F167" s="148"/>
-      <c r="G167" s="148"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="82"/>
-      <c r="B168" s="150" t="s">
-        <v>64</v>
-      </c>
-      <c r="C168" s="114"/>
-      <c r="D168" s="148"/>
-      <c r="E168" s="151" t="s">
-        <v>69</v>
-      </c>
-      <c r="F168" s="151"/>
-      <c r="G168" s="148"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="80"/>
-      <c r="B169" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="C169" s="114"/>
-      <c r="D169" s="148"/>
-      <c r="E169" s="148" t="s">
-        <v>70</v>
-      </c>
-      <c r="F169" s="148"/>
-      <c r="G169" s="148"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="204"/>
-      <c r="B170" s="164"/>
-      <c r="C170" s="164"/>
-      <c r="D170" s="164"/>
-      <c r="E170" s="164"/>
-      <c r="F170" s="164"/>
-      <c r="G170" s="164"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="204"/>
-      <c r="B171" s="164"/>
-      <c r="C171" s="164"/>
-      <c r="D171" s="164"/>
-      <c r="E171" s="164"/>
-      <c r="F171" s="164"/>
-      <c r="G171" s="164"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="204"/>
-      <c r="B172" s="164"/>
-      <c r="C172" s="164"/>
-      <c r="D172" s="164"/>
-      <c r="E172" s="164"/>
-      <c r="F172" s="164"/>
-      <c r="G172" s="164"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="204"/>
-      <c r="B173" s="164"/>
-      <c r="C173" s="164"/>
-      <c r="D173" s="164"/>
-      <c r="E173" s="164"/>
-      <c r="F173" s="164"/>
-      <c r="G173" s="164"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="204"/>
-      <c r="B174" s="164"/>
-      <c r="C174" s="164"/>
-      <c r="D174" s="164"/>
-      <c r="E174" s="164"/>
-      <c r="F174" s="164"/>
-      <c r="G174" s="164"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="204"/>
-      <c r="B175" s="164"/>
-      <c r="C175" s="164"/>
-      <c r="D175" s="164"/>
-      <c r="E175" s="164"/>
-      <c r="F175" s="164"/>
-      <c r="G175" s="164"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="204"/>
-      <c r="B176" s="164"/>
-      <c r="C176" s="164"/>
-      <c r="D176" s="164"/>
-      <c r="E176" s="164"/>
-      <c r="F176" s="164"/>
-      <c r="G176" s="164"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="204"/>
-      <c r="B177" s="164"/>
-      <c r="C177" s="164"/>
-      <c r="D177" s="164"/>
-      <c r="E177" s="164"/>
-      <c r="F177" s="164"/>
-      <c r="G177" s="164"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="E163:F163"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/BKU 2026.xlsx
+++ b/BKU 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\SistemLaporanBarang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B7188D-3737-46E6-A791-923A0D80423B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87F6973-2573-41FB-BFAC-A6C154862862}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANUARI" sheetId="21" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">JANUARI!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6802,7 +6803,7 @@
         <v>51977300</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A85" s="89">
         <v>51</v>
       </c>
@@ -6928,7 +6929,7 @@
       <c r="F91" s="21"/>
       <c r="G91" s="82"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A92" s="89">
         <v>56</v>
       </c>
